--- a/Report JSS 1E.xlsx
+++ b/Report JSS 1E.xlsx
@@ -1,14 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PythonSetup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="3" r:id="rId1"/>
-    <sheet name="Comments" sheetId="4" r:id="rId2"/>
+    <sheet name="Comments" sheetId="4" r:id="rId1"/>
+    <sheet name="Data" sheetId="3" r:id="rId2"/>
     <sheet name="Behaviour" sheetId="5" r:id="rId3"/>
     <sheet name="Skills" sheetId="6" r:id="rId4"/>
     <sheet name="Scoresheet" sheetId="2" r:id="rId5"/>
@@ -19,13 +24,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Report!$A$2:$N$57</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="229">
   <si>
     <t xml:space="preserve">Names </t>
   </si>
@@ -645,9 +649,6 @@
     <t>mungoparkwakul@gmail.com</t>
   </si>
   <si>
-    <t>abubasiddiq@yahoo.com</t>
-  </si>
-  <si>
     <t>ABRAHAM MAMMAN</t>
   </si>
   <si>
@@ -709,6 +710,12 @@
   </si>
   <si>
     <t>JSS1E</t>
+  </si>
+  <si>
+    <t>MUNGOPARK MARVELOUS</t>
+  </si>
+  <si>
+    <t>IDRIS ALKALI IDRIS</t>
   </si>
 </sst>
 </file>
@@ -3997,6 +4004,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:C51" totalsRowShown="0">
+  <autoFilter ref="A1:C51"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Admission_No" dataDxfId="45"/>
+    <tableColumn id="2" name="Comments" dataDxfId="44"/>
+    <tableColumn id="3" name="Position of authourity" dataDxfId="43"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
   <autoFilter ref="A1:J53"/>
   <tableColumns count="10">
@@ -4010,18 +4029,6 @@
     <tableColumn id="8" name="Next Term Begins" dataDxfId="48"/>
     <tableColumn id="9" name="Password" dataDxfId="47"/>
     <tableColumn id="10" name="Email" dataDxfId="46"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:C51" totalsRowShown="0">
-  <autoFilter ref="A1:C51"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Admission_No" dataDxfId="45"/>
-    <tableColumn id="2" name="Comments" dataDxfId="44"/>
-    <tableColumn id="3" name="Position of authourity" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4391,6 +4398,588 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" style="165" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="168" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="182">
+        <v>1</v>
+      </c>
+      <c r="B2" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="182">
+        <v>2</v>
+      </c>
+      <c r="B3" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="182">
+        <v>3</v>
+      </c>
+      <c r="B4" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="182">
+        <v>4</v>
+      </c>
+      <c r="B5" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="182">
+        <v>5</v>
+      </c>
+      <c r="B6" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="182">
+        <v>6</v>
+      </c>
+      <c r="B7" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="182">
+        <v>7</v>
+      </c>
+      <c r="B8" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="182">
+        <v>8</v>
+      </c>
+      <c r="B9" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="182">
+        <v>9</v>
+      </c>
+      <c r="B10" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="182">
+        <v>10</v>
+      </c>
+      <c r="B11" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="182">
+        <v>11</v>
+      </c>
+      <c r="B12" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="182">
+        <v>12</v>
+      </c>
+      <c r="B13" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="182">
+        <v>13</v>
+      </c>
+      <c r="B14" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="182">
+        <v>14</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="182">
+        <v>15</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="182">
+        <v>16</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="182">
+        <v>17</v>
+      </c>
+      <c r="B18" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="182">
+        <v>18</v>
+      </c>
+      <c r="B19" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="182">
+        <v>19</v>
+      </c>
+      <c r="B20" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="182">
+        <v>20</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="182">
+        <v>21</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="182">
+        <v>22</v>
+      </c>
+      <c r="B23" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="182">
+        <v>23</v>
+      </c>
+      <c r="B24" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="182">
+        <v>24</v>
+      </c>
+      <c r="B25" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="182">
+        <v>25</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="182">
+        <v>26</v>
+      </c>
+      <c r="B27" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="182">
+        <v>27</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="182">
+        <v>28</v>
+      </c>
+      <c r="B29" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="182">
+        <v>29</v>
+      </c>
+      <c r="B30" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="182">
+        <v>30</v>
+      </c>
+      <c r="B31" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="182">
+        <v>31</v>
+      </c>
+      <c r="B32" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="182">
+        <v>32</v>
+      </c>
+      <c r="B33" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="182">
+        <v>33</v>
+      </c>
+      <c r="B34" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="182">
+        <v>34</v>
+      </c>
+      <c r="B35" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="182">
+        <v>35</v>
+      </c>
+      <c r="B36" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="182">
+        <v>36</v>
+      </c>
+      <c r="B37" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="182">
+        <v>37</v>
+      </c>
+      <c r="B38" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="182">
+        <v>38</v>
+      </c>
+      <c r="B39" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="182">
+        <v>39</v>
+      </c>
+      <c r="B40" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="182">
+        <v>40</v>
+      </c>
+      <c r="B41" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="182">
+        <v>41</v>
+      </c>
+      <c r="B42" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="182">
+        <v>42</v>
+      </c>
+      <c r="B43" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="182">
+        <v>43</v>
+      </c>
+      <c r="B44" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="182">
+        <v>44</v>
+      </c>
+      <c r="B45" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="182">
+        <v>45</v>
+      </c>
+      <c r="B46" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="182">
+        <v>46</v>
+      </c>
+      <c r="B47" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="182">
+        <v>47</v>
+      </c>
+      <c r="B48" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="182">
+        <v>48</v>
+      </c>
+      <c r="B49" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="182">
+        <v>49</v>
+      </c>
+      <c r="B50" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="174"/>
+      <c r="B51" s="133"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="174"/>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="174"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -4469,7 +5058,7 @@
         <v>3411</v>
       </c>
       <c r="J2" s="208" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4529,7 +5118,7 @@
         <v>3413</v>
       </c>
       <c r="J4" s="189" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4593,7 +5182,7 @@
         <v>3415</v>
       </c>
       <c r="J6" s="189" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4685,7 +5274,7 @@
         <v>3418</v>
       </c>
       <c r="J9" s="189" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5239,7 +5828,7 @@
         <v>3436</v>
       </c>
       <c r="J27" s="189" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5525,7 +6114,7 @@
         <v>3445</v>
       </c>
       <c r="J36" s="189" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -5653,7 +6242,7 @@
         <v>3449</v>
       </c>
       <c r="J40" s="189" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -5689,7 +6278,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="175" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C42" s="167" t="s">
         <v>96</v>
@@ -5715,7 +6304,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="175" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C43" s="167" t="s">
         <v>96</v>
@@ -5735,7 +6324,7 @@
         <v>3452</v>
       </c>
       <c r="J43" s="189" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -5743,7 +6332,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="175" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C44" s="167" t="s">
         <v>96</v>
@@ -5907,624 +6496,42 @@
   <phoneticPr fontId="12" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J32" r:id="rId1"/>
-    <hyperlink ref="J36" r:id="rId2"/>
-    <hyperlink ref="J39" r:id="rId3"/>
-    <hyperlink ref="J28" r:id="rId4"/>
-    <hyperlink ref="J33" r:id="rId5"/>
-    <hyperlink ref="J29" r:id="rId6"/>
-    <hyperlink ref="J24" r:id="rId7"/>
-    <hyperlink ref="J12" r:id="rId8"/>
-    <hyperlink ref="J7" r:id="rId9"/>
-    <hyperlink ref="J31" r:id="rId10"/>
-    <hyperlink ref="J35" r:id="rId11"/>
-    <hyperlink ref="J27" r:id="rId12"/>
-    <hyperlink ref="J41" r:id="rId13"/>
-    <hyperlink ref="J34" r:id="rId14"/>
-    <hyperlink ref="J20" r:id="rId15"/>
-    <hyperlink ref="J18" r:id="rId16"/>
-    <hyperlink ref="J10" r:id="rId17"/>
-    <hyperlink ref="J25" r:id="rId18"/>
-    <hyperlink ref="J5" r:id="rId19"/>
-    <hyperlink ref="J15" r:id="rId20"/>
-    <hyperlink ref="J30" r:id="rId21"/>
-    <hyperlink ref="J22" r:id="rId22"/>
-    <hyperlink ref="J26" r:id="rId23"/>
-    <hyperlink ref="J13" r:id="rId24"/>
-    <hyperlink ref="J38" r:id="rId25"/>
-    <hyperlink ref="J37" r:id="rId26"/>
-    <hyperlink ref="J6" r:id="rId27"/>
-    <hyperlink ref="J43" r:id="rId28"/>
-    <hyperlink ref="J40" r:id="rId29"/>
-    <hyperlink ref="J9" r:id="rId30"/>
-    <hyperlink ref="J4" r:id="rId31"/>
-    <hyperlink ref="J2" r:id="rId32"/>
+    <hyperlink ref="J39" r:id="rId2"/>
+    <hyperlink ref="J28" r:id="rId3"/>
+    <hyperlink ref="J33" r:id="rId4"/>
+    <hyperlink ref="J29" r:id="rId5"/>
+    <hyperlink ref="J24" r:id="rId6"/>
+    <hyperlink ref="J12" r:id="rId7"/>
+    <hyperlink ref="J7" r:id="rId8"/>
+    <hyperlink ref="J31" r:id="rId9"/>
+    <hyperlink ref="J35" r:id="rId10"/>
+    <hyperlink ref="J36" r:id="rId11"/>
+    <hyperlink ref="J41" r:id="rId12"/>
+    <hyperlink ref="J34" r:id="rId13"/>
+    <hyperlink ref="J20" r:id="rId14"/>
+    <hyperlink ref="J18" r:id="rId15"/>
+    <hyperlink ref="J10" r:id="rId16"/>
+    <hyperlink ref="J25" r:id="rId17"/>
+    <hyperlink ref="J5" r:id="rId18"/>
+    <hyperlink ref="J15" r:id="rId19"/>
+    <hyperlink ref="J30" r:id="rId20"/>
+    <hyperlink ref="J22" r:id="rId21"/>
+    <hyperlink ref="J26" r:id="rId22"/>
+    <hyperlink ref="J13" r:id="rId23"/>
+    <hyperlink ref="J38" r:id="rId24"/>
+    <hyperlink ref="J37" r:id="rId25"/>
+    <hyperlink ref="J43" r:id="rId26"/>
+    <hyperlink ref="J40" r:id="rId27"/>
+    <hyperlink ref="J9" r:id="rId28"/>
+    <hyperlink ref="J4" r:id="rId29"/>
+    <hyperlink ref="J2" r:id="rId30"/>
+    <hyperlink ref="J6" r:id="rId31" display="abubasiddiq@yahoo.com"/>
+    <hyperlink ref="J27" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId33"/>
   <tableParts count="1">
     <tablePart r:id="rId34"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22.28515625" style="165" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="168" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="182">
-        <v>1</v>
-      </c>
-      <c r="B2" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="182">
-        <v>2</v>
-      </c>
-      <c r="B3" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="182">
-        <v>3</v>
-      </c>
-      <c r="B4" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="182">
-        <v>4</v>
-      </c>
-      <c r="B5" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="182">
-        <v>5</v>
-      </c>
-      <c r="B6" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="182">
-        <v>6</v>
-      </c>
-      <c r="B7" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="182">
-        <v>7</v>
-      </c>
-      <c r="B8" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="182">
-        <v>8</v>
-      </c>
-      <c r="B9" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="182">
-        <v>9</v>
-      </c>
-      <c r="B10" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="182">
-        <v>10</v>
-      </c>
-      <c r="B11" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="182">
-        <v>11</v>
-      </c>
-      <c r="B12" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="182">
-        <v>12</v>
-      </c>
-      <c r="B13" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="182">
-        <v>13</v>
-      </c>
-      <c r="B14" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="182">
-        <v>14</v>
-      </c>
-      <c r="B15" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="182">
-        <v>15</v>
-      </c>
-      <c r="B16" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="182">
-        <v>16</v>
-      </c>
-      <c r="B17" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="182">
-        <v>17</v>
-      </c>
-      <c r="B18" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="182">
-        <v>18</v>
-      </c>
-      <c r="B19" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="182">
-        <v>19</v>
-      </c>
-      <c r="B20" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="182">
-        <v>20</v>
-      </c>
-      <c r="B21" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="182">
-        <v>21</v>
-      </c>
-      <c r="B22" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="182">
-        <v>22</v>
-      </c>
-      <c r="B23" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="182">
-        <v>23</v>
-      </c>
-      <c r="B24" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="182">
-        <v>24</v>
-      </c>
-      <c r="B25" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="182">
-        <v>25</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="182">
-        <v>26</v>
-      </c>
-      <c r="B27" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="182">
-        <v>27</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="182">
-        <v>28</v>
-      </c>
-      <c r="B29" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="182">
-        <v>29</v>
-      </c>
-      <c r="B30" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="182">
-        <v>30</v>
-      </c>
-      <c r="B31" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="182">
-        <v>31</v>
-      </c>
-      <c r="B32" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="182">
-        <v>32</v>
-      </c>
-      <c r="B33" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="182">
-        <v>33</v>
-      </c>
-      <c r="B34" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="182">
-        <v>34</v>
-      </c>
-      <c r="B35" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="182">
-        <v>35</v>
-      </c>
-      <c r="B36" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="182">
-        <v>36</v>
-      </c>
-      <c r="B37" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="182">
-        <v>37</v>
-      </c>
-      <c r="B38" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="182">
-        <v>38</v>
-      </c>
-      <c r="B39" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="182">
-        <v>39</v>
-      </c>
-      <c r="B40" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="182">
-        <v>40</v>
-      </c>
-      <c r="B41" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="182">
-        <v>41</v>
-      </c>
-      <c r="B42" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="182">
-        <v>42</v>
-      </c>
-      <c r="B43" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="182">
-        <v>43</v>
-      </c>
-      <c r="B44" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="182">
-        <v>44</v>
-      </c>
-      <c r="B45" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="182">
-        <v>45</v>
-      </c>
-      <c r="B46" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="182">
-        <v>46</v>
-      </c>
-      <c r="B47" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="182">
-        <v>47</v>
-      </c>
-      <c r="B48" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="182">
-        <v>48</v>
-      </c>
-      <c r="B49" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="182">
-        <v>49</v>
-      </c>
-      <c r="B50" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="174"/>
-      <c r="B51" s="133"/>
-      <c r="C51" s="3"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="174"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="174"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45291,7 +45298,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="146" customFormat="1" ht="36" customHeight="1">
       <c r="A1" s="280" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B1" s="281"/>
       <c r="C1" s="281"/>
@@ -45323,10 +45330,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="210" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="283" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" s="283"/>
       <c r="D3" s="283"/>
@@ -45341,7 +45348,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="277" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B4" s="278"/>
       <c r="C4" s="278"/>
@@ -45355,33 +45362,33 @@
       <c r="K4" s="278"/>
       <c r="L4" s="279"/>
     </row>
-    <row r="5" spans="1:12" ht="106.5">
+    <row r="5" spans="1:12" ht="105.75">
       <c r="A5" s="211" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="212" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="212" t="s">
+      <c r="C5" s="213" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="D5" s="213" t="s">
         <v>220</v>
       </c>
-      <c r="D5" s="213" t="s">
+      <c r="E5" s="213" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="213" t="s">
+      <c r="F5" s="213" t="s">
         <v>222</v>
       </c>
-      <c r="F5" s="213" t="s">
+      <c r="G5" s="213" t="s">
         <v>223</v>
       </c>
-      <c r="G5" s="213" t="s">
+      <c r="H5" s="213" t="s">
         <v>224</v>
       </c>
-      <c r="H5" s="213" t="s">
+      <c r="I5" s="213" t="s">
         <v>225</v>
-      </c>
-      <c r="I5" s="213" t="s">
-        <v>226</v>
       </c>
       <c r="J5" s="213" t="s">
         <v>16</v>
@@ -46356,7 +46363,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="209" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="C38" s="216"/>
       <c r="D38" s="216"/>
@@ -46506,7 +46513,7 @@
         <v>38</v>
       </c>
       <c r="B43" s="209" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C43" s="216"/>
       <c r="D43" s="216"/>
@@ -46536,7 +46543,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="209" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="216"/>
       <c r="D44" s="216"/>
@@ -46566,7 +46573,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="209" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="216"/>
       <c r="D45" s="216"/>
@@ -46595,7 +46602,9 @@
       <c r="A46" s="215">
         <v>41</v>
       </c>
-      <c r="B46" s="209"/>
+      <c r="B46" s="209" t="s">
+        <v>228</v>
+      </c>
       <c r="C46" s="216"/>
       <c r="D46" s="216"/>
       <c r="E46" s="216"/>
@@ -46917,7 +46926,7 @@
     <col min="21" max="22" width="11.140625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="75">
+    <row r="1" spans="1:22" ht="74.25">
       <c r="A1" s="166" t="s">
         <v>177</v>
       </c>

--- a/Report JSS 1E.xlsx
+++ b/Report JSS 1E.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="230">
   <si>
     <t xml:space="preserve">Names </t>
   </si>
@@ -718,7 +718,7 @@
     <t>IDRIS ALKALI IDRIS</t>
   </si>
   <si>
-    <t>ABRAHAM MAMMAN palna,</t>
+    <t>ABRAHAM MAMMAN PALNAM</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1643,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2125,11 +2125,41 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2146,82 +2176,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2250,6 +2206,50 @@
     <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2270,6 +2270,9 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Hyperlink" xfId="19" builtinId="8"/>
@@ -3540,7 +3543,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3631,7 +3634,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3727,7 +3730,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9187,14 +9190,14 @@
   <sheetData>
     <row r="1" spans="1:216">
       <c r="A1" s="41"/>
-      <c r="B1" s="222" t="s">
+      <c r="B1" s="233" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
       <c r="H1" s="49"/>
       <c r="I1" s="49"/>
       <c r="J1" s="50"/>
@@ -9203,28 +9206,28 @@
       <c r="M1" s="41"/>
       <c r="N1" s="56"/>
       <c r="O1" s="55"/>
-      <c r="P1" s="227" t="s">
+      <c r="P1" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="228"/>
-      <c r="R1" s="228"/>
-      <c r="S1" s="228"/>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
+      <c r="Q1" s="238"/>
+      <c r="R1" s="238"/>
+      <c r="S1" s="238"/>
+      <c r="T1" s="238"/>
+      <c r="U1" s="238"/>
+      <c r="V1" s="238"/>
       <c r="W1" s="57"/>
       <c r="X1" s="57"/>
       <c r="Y1" s="54"/>
       <c r="Z1" s="79"/>
-      <c r="AA1" s="223" t="s">
+      <c r="AA1" s="227" t="s">
         <v>103</v>
       </c>
-      <c r="AB1" s="223"/>
-      <c r="AC1" s="223"/>
-      <c r="AD1" s="223"/>
-      <c r="AE1" s="223"/>
-      <c r="AF1" s="223"/>
-      <c r="AG1" s="223"/>
+      <c r="AB1" s="227"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="227"/>
+      <c r="AE1" s="227"/>
+      <c r="AF1" s="227"/>
+      <c r="AG1" s="227"/>
       <c r="AH1" s="79"/>
       <c r="AI1" s="79"/>
       <c r="AJ1" s="79"/>
@@ -9244,197 +9247,197 @@
       <c r="AV1" s="44"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="85"/>
-      <c r="AY1" s="224" t="s">
+      <c r="AY1" s="234" t="s">
         <v>92</v>
       </c>
-      <c r="AZ1" s="224"/>
-      <c r="BA1" s="224"/>
-      <c r="BB1" s="224"/>
-      <c r="BC1" s="224"/>
-      <c r="BD1" s="224"/>
-      <c r="BE1" s="224"/>
+      <c r="AZ1" s="234"/>
+      <c r="BA1" s="234"/>
+      <c r="BB1" s="234"/>
+      <c r="BC1" s="234"/>
+      <c r="BD1" s="234"/>
+      <c r="BE1" s="234"/>
       <c r="BF1" s="85"/>
       <c r="BG1" s="85"/>
       <c r="BH1" s="85"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="90"/>
-      <c r="BK1" s="225" t="s">
+      <c r="BK1" s="235" t="s">
         <v>63</v>
       </c>
-      <c r="BL1" s="226"/>
-      <c r="BM1" s="226"/>
-      <c r="BN1" s="226"/>
-      <c r="BO1" s="226"/>
-      <c r="BP1" s="226"/>
-      <c r="BQ1" s="226"/>
+      <c r="BL1" s="236"/>
+      <c r="BM1" s="236"/>
+      <c r="BN1" s="236"/>
+      <c r="BO1" s="236"/>
+      <c r="BP1" s="236"/>
+      <c r="BQ1" s="236"/>
       <c r="BR1" s="90"/>
       <c r="BS1" s="90"/>
       <c r="BT1" s="90"/>
       <c r="BU1" s="3"/>
       <c r="BV1" s="95"/>
-      <c r="BW1" s="229" t="s">
+      <c r="BW1" s="228" t="s">
         <v>86</v>
       </c>
-      <c r="BX1" s="229"/>
-      <c r="BY1" s="229"/>
-      <c r="BZ1" s="229"/>
-      <c r="CA1" s="229"/>
-      <c r="CB1" s="229"/>
-      <c r="CC1" s="229"/>
+      <c r="BX1" s="228"/>
+      <c r="BY1" s="228"/>
+      <c r="BZ1" s="228"/>
+      <c r="CA1" s="228"/>
+      <c r="CB1" s="228"/>
+      <c r="CC1" s="228"/>
       <c r="CD1" s="95"/>
       <c r="CE1" s="95"/>
       <c r="CF1" s="95"/>
       <c r="CG1" s="3"/>
       <c r="CH1" s="64"/>
-      <c r="CI1" s="230" t="s">
+      <c r="CI1" s="229" t="s">
         <v>87</v>
       </c>
-      <c r="CJ1" s="230"/>
-      <c r="CK1" s="230"/>
-      <c r="CL1" s="230"/>
-      <c r="CM1" s="230"/>
-      <c r="CN1" s="230"/>
-      <c r="CO1" s="230"/>
+      <c r="CJ1" s="229"/>
+      <c r="CK1" s="229"/>
+      <c r="CL1" s="229"/>
+      <c r="CM1" s="229"/>
+      <c r="CN1" s="229"/>
+      <c r="CO1" s="229"/>
       <c r="CP1" s="64"/>
       <c r="CQ1" s="64"/>
       <c r="CR1" s="64"/>
       <c r="CS1" s="3"/>
       <c r="CT1" s="69"/>
-      <c r="CU1" s="231" t="s">
+      <c r="CU1" s="230" t="s">
         <v>66</v>
       </c>
-      <c r="CV1" s="231"/>
-      <c r="CW1" s="231"/>
-      <c r="CX1" s="231"/>
-      <c r="CY1" s="231"/>
-      <c r="CZ1" s="231"/>
-      <c r="DA1" s="231"/>
+      <c r="CV1" s="230"/>
+      <c r="CW1" s="230"/>
+      <c r="CX1" s="230"/>
+      <c r="CY1" s="230"/>
+      <c r="CZ1" s="230"/>
+      <c r="DA1" s="230"/>
       <c r="DB1" s="69"/>
       <c r="DC1" s="69"/>
       <c r="DD1" s="69"/>
       <c r="DE1" s="3"/>
       <c r="DF1" s="56"/>
-      <c r="DG1" s="232" t="s">
+      <c r="DG1" s="231" t="s">
         <v>88</v>
       </c>
-      <c r="DH1" s="232"/>
-      <c r="DI1" s="232"/>
-      <c r="DJ1" s="232"/>
-      <c r="DK1" s="232"/>
-      <c r="DL1" s="232"/>
-      <c r="DM1" s="232"/>
+      <c r="DH1" s="231"/>
+      <c r="DI1" s="231"/>
+      <c r="DJ1" s="231"/>
+      <c r="DK1" s="231"/>
+      <c r="DL1" s="231"/>
+      <c r="DM1" s="231"/>
       <c r="DN1" s="56"/>
       <c r="DO1" s="56"/>
       <c r="DP1" s="56"/>
       <c r="DQ1" s="3"/>
       <c r="DR1" s="105"/>
-      <c r="DS1" s="233" t="s">
+      <c r="DS1" s="232" t="s">
         <v>89</v>
       </c>
-      <c r="DT1" s="233"/>
-      <c r="DU1" s="233"/>
-      <c r="DV1" s="233"/>
-      <c r="DW1" s="233"/>
-      <c r="DX1" s="233"/>
-      <c r="DY1" s="233"/>
+      <c r="DT1" s="232"/>
+      <c r="DU1" s="232"/>
+      <c r="DV1" s="232"/>
+      <c r="DW1" s="232"/>
+      <c r="DX1" s="232"/>
+      <c r="DY1" s="232"/>
       <c r="DZ1" s="105"/>
       <c r="EA1" s="105"/>
       <c r="EB1" s="105"/>
       <c r="EC1" s="3"/>
       <c r="ED1" s="74"/>
-      <c r="EE1" s="236" t="s">
+      <c r="EE1" s="224" t="s">
         <v>64</v>
       </c>
-      <c r="EF1" s="236"/>
-      <c r="EG1" s="236"/>
-      <c r="EH1" s="236"/>
-      <c r="EI1" s="236"/>
-      <c r="EJ1" s="236"/>
-      <c r="EK1" s="236"/>
+      <c r="EF1" s="224"/>
+      <c r="EG1" s="224"/>
+      <c r="EH1" s="224"/>
+      <c r="EI1" s="224"/>
+      <c r="EJ1" s="224"/>
+      <c r="EK1" s="224"/>
       <c r="EL1" s="74"/>
       <c r="EM1" s="74"/>
       <c r="EN1" s="74"/>
       <c r="EO1" s="3"/>
       <c r="EP1" s="100"/>
-      <c r="EQ1" s="237" t="s">
+      <c r="EQ1" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="ER1" s="237"/>
-      <c r="ES1" s="237"/>
-      <c r="ET1" s="237"/>
-      <c r="EU1" s="237"/>
-      <c r="EV1" s="237"/>
-      <c r="EW1" s="237"/>
+      <c r="ER1" s="225"/>
+      <c r="ES1" s="225"/>
+      <c r="ET1" s="225"/>
+      <c r="EU1" s="225"/>
+      <c r="EV1" s="225"/>
+      <c r="EW1" s="225"/>
       <c r="EX1" s="100"/>
       <c r="EY1" s="100"/>
       <c r="EZ1" s="100"/>
       <c r="FA1" s="3"/>
       <c r="FB1" s="116"/>
-      <c r="FC1" s="235" t="s">
+      <c r="FC1" s="223" t="s">
         <v>65</v>
       </c>
-      <c r="FD1" s="235"/>
-      <c r="FE1" s="235"/>
-      <c r="FF1" s="235"/>
-      <c r="FG1" s="235"/>
-      <c r="FH1" s="235"/>
-      <c r="FI1" s="235"/>
+      <c r="FD1" s="223"/>
+      <c r="FE1" s="223"/>
+      <c r="FF1" s="223"/>
+      <c r="FG1" s="223"/>
+      <c r="FH1" s="223"/>
+      <c r="FI1" s="223"/>
       <c r="FJ1" s="116"/>
       <c r="FK1" s="116"/>
       <c r="FL1" s="116"/>
       <c r="FM1" s="3"/>
       <c r="FN1" s="50"/>
-      <c r="FO1" s="238" t="s">
+      <c r="FO1" s="226" t="s">
         <v>93</v>
       </c>
-      <c r="FP1" s="238"/>
-      <c r="FQ1" s="238"/>
-      <c r="FR1" s="238"/>
-      <c r="FS1" s="238"/>
-      <c r="FT1" s="238"/>
-      <c r="FU1" s="238"/>
+      <c r="FP1" s="226"/>
+      <c r="FQ1" s="226"/>
+      <c r="FR1" s="226"/>
+      <c r="FS1" s="226"/>
+      <c r="FT1" s="226"/>
+      <c r="FU1" s="226"/>
       <c r="FV1" s="50"/>
       <c r="FW1" s="50"/>
       <c r="FX1" s="50"/>
       <c r="FY1" s="3"/>
       <c r="FZ1" s="79"/>
-      <c r="GA1" s="223" t="s">
+      <c r="GA1" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="GB1" s="223"/>
-      <c r="GC1" s="223"/>
-      <c r="GD1" s="223"/>
-      <c r="GE1" s="223"/>
-      <c r="GF1" s="223"/>
-      <c r="GG1" s="223"/>
+      <c r="GB1" s="227"/>
+      <c r="GC1" s="227"/>
+      <c r="GD1" s="227"/>
+      <c r="GE1" s="227"/>
+      <c r="GF1" s="227"/>
+      <c r="GG1" s="227"/>
       <c r="GH1" s="79"/>
       <c r="GI1" s="79"/>
       <c r="GJ1" s="79"/>
       <c r="GK1" s="3"/>
       <c r="GL1" s="116"/>
-      <c r="GM1" s="235" t="s">
+      <c r="GM1" s="223" t="s">
         <v>62</v>
       </c>
-      <c r="GN1" s="235"/>
-      <c r="GO1" s="235"/>
-      <c r="GP1" s="235"/>
-      <c r="GQ1" s="235"/>
-      <c r="GR1" s="235"/>
-      <c r="GS1" s="235"/>
+      <c r="GN1" s="223"/>
+      <c r="GO1" s="223"/>
+      <c r="GP1" s="223"/>
+      <c r="GQ1" s="223"/>
+      <c r="GR1" s="223"/>
+      <c r="GS1" s="223"/>
       <c r="GT1" s="116"/>
       <c r="GU1" s="116"/>
       <c r="GV1" s="116"/>
       <c r="GW1" s="3"/>
       <c r="GX1" s="110"/>
-      <c r="GY1" s="234" t="s">
+      <c r="GY1" s="222" t="s">
         <v>82</v>
       </c>
-      <c r="GZ1" s="234"/>
-      <c r="HA1" s="234"/>
-      <c r="HB1" s="234"/>
-      <c r="HC1" s="234"/>
-      <c r="HD1" s="234"/>
-      <c r="HE1" s="234"/>
+      <c r="GZ1" s="222"/>
+      <c r="HA1" s="222"/>
+      <c r="HB1" s="222"/>
+      <c r="HC1" s="222"/>
+      <c r="HD1" s="222"/>
+      <c r="HE1" s="222"/>
       <c r="HF1" s="110"/>
       <c r="HG1" s="110"/>
       <c r="HH1" s="110"/>
@@ -37736,8 +37739,12 @@
       </c>
     </row>
     <row r="43" spans="1:216" ht="18">
-      <c r="A43" s="41"/>
-      <c r="B43" s="163"/>
+      <c r="A43" s="183">
+        <v>41</v>
+      </c>
+      <c r="B43" s="285" t="s">
+        <v>229</v>
+      </c>
       <c r="C43" s="130">
         <v>3</v>
       </c>
@@ -38428,8 +38435,12 @@
       </c>
     </row>
     <row r="44" spans="1:216" ht="18">
-      <c r="A44" s="41"/>
-      <c r="B44" s="163"/>
+      <c r="A44" s="183">
+        <v>42</v>
+      </c>
+      <c r="B44" s="132" t="s">
+        <v>207</v>
+      </c>
       <c r="C44" s="144">
         <v>1</v>
       </c>
@@ -39108,8 +39119,12 @@
       </c>
     </row>
     <row r="45" spans="1:216" ht="18">
-      <c r="A45" s="41"/>
-      <c r="B45" s="163"/>
+      <c r="A45" s="183">
+        <v>43</v>
+      </c>
+      <c r="B45" s="285" t="s">
+        <v>208</v>
+      </c>
       <c r="C45" s="144">
         <v>1</v>
       </c>
@@ -43410,6 +43425,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AY1:BE1"/>
+    <mergeCell ref="BK1:BQ1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="BW1:CC1"/>
+    <mergeCell ref="CI1:CO1"/>
+    <mergeCell ref="CU1:DA1"/>
+    <mergeCell ref="DG1:DM1"/>
+    <mergeCell ref="DS1:DY1"/>
     <mergeCell ref="GY1:HE1"/>
     <mergeCell ref="GM1:GS1"/>
     <mergeCell ref="EE1:EK1"/>
@@ -43417,16 +43442,6 @@
     <mergeCell ref="FC1:FI1"/>
     <mergeCell ref="FO1:FU1"/>
     <mergeCell ref="GA1:GG1"/>
-    <mergeCell ref="BW1:CC1"/>
-    <mergeCell ref="CI1:CO1"/>
-    <mergeCell ref="CU1:DA1"/>
-    <mergeCell ref="DG1:DM1"/>
-    <mergeCell ref="DS1:DY1"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AY1:BE1"/>
-    <mergeCell ref="BK1:BQ1"/>
-    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43588,114 +43603,114 @@
       <c r="A10" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="239" t="str">
+      <c r="B10" s="273" t="str">
         <f>VLOOKUP(B14,Data!A1:I53,2,0)</f>
         <v>AKILAHYEL SUCCESS GWANDI</v>
       </c>
-      <c r="C10" s="239"/>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
+      <c r="C10" s="273"/>
+      <c r="D10" s="273"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="273"/>
+      <c r="G10" s="273"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
-      <c r="K10" s="240" t="s">
+      <c r="K10" s="271" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="240"/>
-      <c r="M10" s="239" t="str">
+      <c r="L10" s="271"/>
+      <c r="M10" s="273" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,7,0)</f>
         <v xml:space="preserve">1st </v>
       </c>
-      <c r="N10" s="241"/>
+      <c r="N10" s="274"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="240">
+      <c r="B11" s="271">
         <f>VLOOKUP(B14,Data!A2:H53,4,0)</f>
         <v>10</v>
       </c>
-      <c r="C11" s="240"/>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
+      <c r="C11" s="271"/>
+      <c r="D11" s="271"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
       <c r="H11" s="29"/>
       <c r="I11" s="29"/>
       <c r="J11" s="29"/>
-      <c r="K11" s="240" t="s">
+      <c r="K11" s="271" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="240"/>
-      <c r="M11" s="239" t="str">
+      <c r="L11" s="271"/>
+      <c r="M11" s="273" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,3,0)</f>
         <v>JSS 1 E</v>
       </c>
-      <c r="N11" s="241"/>
+      <c r="N11" s="274"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="239" t="str">
+      <c r="B12" s="273" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,5,0)</f>
         <v>BORNO</v>
       </c>
-      <c r="C12" s="239"/>
-      <c r="D12" s="239"/>
-      <c r="E12" s="239"/>
-      <c r="F12" s="239"/>
-      <c r="G12" s="239"/>
+      <c r="C12" s="273"/>
+      <c r="D12" s="273"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="273"/>
+      <c r="G12" s="273"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
-      <c r="K12" s="240" t="s">
+      <c r="K12" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="L12" s="240"/>
-      <c r="M12" s="239" t="str">
+      <c r="L12" s="271"/>
+      <c r="M12" s="273" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,8,0)</f>
         <v>16th January, 2026</v>
       </c>
-      <c r="N12" s="241"/>
+      <c r="N12" s="274"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="239" t="str">
+      <c r="B13" s="273" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,6,0)</f>
         <v>HAWUL</v>
       </c>
-      <c r="C13" s="239"/>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
+      <c r="C13" s="273"/>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273"/>
+      <c r="F13" s="273"/>
+      <c r="G13" s="273"/>
       <c r="H13" s="29"/>
       <c r="I13" s="29"/>
       <c r="J13" s="29"/>
-      <c r="K13" s="240" t="s">
+      <c r="K13" s="271" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="240"/>
-      <c r="M13" s="239" t="str">
+      <c r="L13" s="271"/>
+      <c r="M13" s="273" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="241"/>
+      <c r="N13" s="274"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="240">
+      <c r="B14" s="271">
         <v>24</v>
       </c>
-      <c r="C14" s="240"/>
+      <c r="C14" s="271"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
@@ -43703,10 +43718,10 @@
       <c r="H14" s="29"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
-      <c r="M14" s="239"/>
-      <c r="N14" s="241"/>
+      <c r="K14" s="272"/>
+      <c r="L14" s="272"/>
+      <c r="M14" s="273"/>
+      <c r="N14" s="274"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="34" t="s">
@@ -43724,10 +43739,10 @@
       <c r="H15" s="29"/>
       <c r="I15" s="29"/>
       <c r="J15" s="29"/>
-      <c r="K15" s="243"/>
-      <c r="L15" s="243"/>
-      <c r="M15" s="242"/>
-      <c r="N15" s="244"/>
+      <c r="K15" s="275"/>
+      <c r="L15" s="275"/>
+      <c r="M15" s="272"/>
+      <c r="N15" s="276"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="34" t="s">
@@ -43767,111 +43782,111 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="268" t="s">
+      <c r="A18" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="270" t="s">
+      <c r="B18" s="244" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="270" t="s">
+      <c r="C18" s="244" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="270" t="s">
+      <c r="D18" s="244" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="270" t="s">
+      <c r="E18" s="244" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="272" t="s">
+      <c r="F18" s="246" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="270" t="s">
+      <c r="G18" s="244" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="270" t="s">
+      <c r="H18" s="244" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="272" t="s">
+      <c r="I18" s="246" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="274" t="s">
+      <c r="J18" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="245" t="s">
+      <c r="K18" s="263" t="s">
         <v>53</v>
       </c>
-      <c r="L18" s="246"/>
-      <c r="M18" s="247">
+      <c r="L18" s="264"/>
+      <c r="M18" s="265">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="248"/>
+      <c r="N18" s="266"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="269"/>
-      <c r="B19" s="271"/>
-      <c r="C19" s="271"/>
-      <c r="D19" s="271"/>
-      <c r="E19" s="271"/>
-      <c r="F19" s="273"/>
-      <c r="G19" s="271"/>
-      <c r="H19" s="271"/>
-      <c r="I19" s="273"/>
-      <c r="J19" s="275"/>
-      <c r="K19" s="249" t="s">
+      <c r="A19" s="243"/>
+      <c r="B19" s="245"/>
+      <c r="C19" s="245"/>
+      <c r="D19" s="245"/>
+      <c r="E19" s="245"/>
+      <c r="F19" s="247"/>
+      <c r="G19" s="245"/>
+      <c r="H19" s="245"/>
+      <c r="I19" s="247"/>
+      <c r="J19" s="249"/>
+      <c r="K19" s="267" t="s">
         <v>54</v>
       </c>
-      <c r="L19" s="250"/>
-      <c r="M19" s="251">
+      <c r="L19" s="268"/>
+      <c r="M19" s="255">
         <f>SUM(H23:H40)</f>
         <v>1161</v>
       </c>
-      <c r="N19" s="252"/>
+      <c r="N19" s="256"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="269"/>
-      <c r="B20" s="271"/>
-      <c r="C20" s="271"/>
-      <c r="D20" s="271"/>
-      <c r="E20" s="271"/>
-      <c r="F20" s="273"/>
-      <c r="G20" s="271"/>
-      <c r="H20" s="271"/>
-      <c r="I20" s="273"/>
-      <c r="J20" s="275"/>
-      <c r="K20" s="249" t="s">
+      <c r="A20" s="243"/>
+      <c r="B20" s="245"/>
+      <c r="C20" s="245"/>
+      <c r="D20" s="245"/>
+      <c r="E20" s="245"/>
+      <c r="F20" s="247"/>
+      <c r="G20" s="245"/>
+      <c r="H20" s="245"/>
+      <c r="I20" s="247"/>
+      <c r="J20" s="249"/>
+      <c r="K20" s="267" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="250"/>
-      <c r="M20" s="253">
+      <c r="L20" s="268"/>
+      <c r="M20" s="269">
         <f>VLOOKUP(B14,Bsheet!A2:V51,21,0)</f>
         <v>69</v>
       </c>
-      <c r="N20" s="254"/>
+      <c r="N20" s="270"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="269"/>
-      <c r="B21" s="271"/>
-      <c r="C21" s="271"/>
-      <c r="D21" s="271"/>
-      <c r="E21" s="271"/>
-      <c r="F21" s="273"/>
-      <c r="G21" s="271"/>
-      <c r="H21" s="271"/>
-      <c r="I21" s="273"/>
-      <c r="J21" s="276"/>
-      <c r="K21" s="255" t="s">
+      <c r="A21" s="243"/>
+      <c r="B21" s="245"/>
+      <c r="C21" s="245"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="247"/>
+      <c r="G21" s="245"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="247"/>
+      <c r="J21" s="250"/>
+      <c r="K21" s="257" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="256"/>
-      <c r="M21" s="257">
+      <c r="L21" s="258"/>
+      <c r="M21" s="259">
         <f>VLOOKUP(B14,Bsheet!A2:V51,22,0)</f>
         <v>10</v>
       </c>
-      <c r="N21" s="258"/>
+      <c r="N21" s="260"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="269"/>
+      <c r="A22" s="243"/>
       <c r="B22" s="27" t="s">
         <v>57</v>
       </c>
@@ -43895,12 +43910,12 @@
       </c>
       <c r="I22" s="124"/>
       <c r="J22" s="125"/>
-      <c r="K22" s="259" t="s">
+      <c r="K22" s="261" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="259"/>
-      <c r="M22" s="259"/>
-      <c r="N22" s="260"/>
+      <c r="L22" s="261"/>
+      <c r="M22" s="261"/>
+      <c r="N22" s="262"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="28" t="s">
@@ -43942,13 +43957,13 @@
         <f>VLOOKUP(B14,Scoresheet!A3:K52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K23" s="261" t="str">
+      <c r="K23" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L23" s="251"/>
-      <c r="M23" s="251"/>
-      <c r="N23" s="252"/>
+      <c r="L23" s="255"/>
+      <c r="M23" s="255"/>
+      <c r="N23" s="256"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="28" t="s">
@@ -43990,13 +44005,13 @@
         <f>VLOOKUP(B14,Scoresheet!M3:W52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K24" s="261" t="str">
+      <c r="K24" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!M3:X52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L24" s="251"/>
-      <c r="M24" s="251"/>
-      <c r="N24" s="252"/>
+      <c r="L24" s="255"/>
+      <c r="M24" s="255"/>
+      <c r="N24" s="256"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="28" t="s">
@@ -44038,13 +44053,13 @@
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K25" s="261" t="str">
+      <c r="K25" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y3:AJ52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L25" s="251"/>
-      <c r="M25" s="251"/>
-      <c r="N25" s="252"/>
+      <c r="L25" s="255"/>
+      <c r="M25" s="255"/>
+      <c r="N25" s="256"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="28" t="s">
@@ -44086,13 +44101,13 @@
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="261" t="str">
+      <c r="K26" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK3:AV52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L26" s="251"/>
-      <c r="M26" s="251"/>
-      <c r="N26" s="252"/>
+      <c r="L26" s="255"/>
+      <c r="M26" s="255"/>
+      <c r="N26" s="256"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="28" t="s">
@@ -44134,13 +44149,13 @@
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K27" s="261" t="str">
+      <c r="K27" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW3:BH52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L27" s="251"/>
-      <c r="M27" s="251"/>
-      <c r="N27" s="252"/>
+      <c r="L27" s="255"/>
+      <c r="M27" s="255"/>
+      <c r="N27" s="256"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="28" t="s">
@@ -44182,13 +44197,13 @@
         <f>VLOOKUP(B14,Scoresheet!BI3:BU52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K28" s="261" t="str">
+      <c r="K28" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI3:BT52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L28" s="251"/>
-      <c r="M28" s="251"/>
-      <c r="N28" s="252"/>
+      <c r="L28" s="255"/>
+      <c r="M28" s="255"/>
+      <c r="N28" s="256"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="28" t="s">
@@ -44230,13 +44245,13 @@
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K29" s="261" t="str">
+      <c r="K29" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU3:CF52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L29" s="251"/>
-      <c r="M29" s="251"/>
-      <c r="N29" s="252"/>
+      <c r="L29" s="255"/>
+      <c r="M29" s="255"/>
+      <c r="N29" s="256"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="28" t="s">
@@ -44278,13 +44293,13 @@
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K30" s="261" t="str">
+      <c r="K30" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG3:CR52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L30" s="251"/>
-      <c r="M30" s="251"/>
-      <c r="N30" s="252"/>
+      <c r="L30" s="255"/>
+      <c r="M30" s="255"/>
+      <c r="N30" s="256"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="28" t="s">
@@ -44326,13 +44341,13 @@
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K31" s="261" t="str">
+      <c r="K31" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS3:DD52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L31" s="251"/>
-      <c r="M31" s="251"/>
-      <c r="N31" s="252"/>
+      <c r="L31" s="255"/>
+      <c r="M31" s="255"/>
+      <c r="N31" s="256"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="28" t="s">
@@ -44374,13 +44389,13 @@
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K32" s="261" t="str">
+      <c r="K32" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE3:DP52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L32" s="251"/>
-      <c r="M32" s="251"/>
-      <c r="N32" s="252"/>
+      <c r="L32" s="255"/>
+      <c r="M32" s="255"/>
+      <c r="N32" s="256"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="28" t="s">
@@ -44422,13 +44437,13 @@
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K33" s="261" t="str">
+      <c r="K33" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EB52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L33" s="251"/>
-      <c r="M33" s="251"/>
-      <c r="N33" s="252"/>
+      <c r="L33" s="255"/>
+      <c r="M33" s="255"/>
+      <c r="N33" s="256"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="28" t="s">
@@ -44470,13 +44485,13 @@
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K34" s="261" t="str">
+      <c r="K34" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC3:EN52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L34" s="251"/>
-      <c r="M34" s="251"/>
-      <c r="N34" s="252"/>
+      <c r="L34" s="255"/>
+      <c r="M34" s="255"/>
+      <c r="N34" s="256"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="28" t="s">
@@ -44518,13 +44533,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K35" s="261" t="str">
+      <c r="K35" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EZ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L35" s="251"/>
-      <c r="M35" s="251"/>
-      <c r="N35" s="252"/>
+      <c r="L35" s="255"/>
+      <c r="M35" s="255"/>
+      <c r="N35" s="256"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="28" t="s">
@@ -44566,13 +44581,13 @@
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,11,0)</f>
         <v>P</v>
       </c>
-      <c r="K36" s="261" t="str">
+      <c r="K36" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA3:FL52,12,0)</f>
         <v>Pass</v>
       </c>
-      <c r="L36" s="251"/>
-      <c r="M36" s="251"/>
-      <c r="N36" s="252"/>
+      <c r="L36" s="255"/>
+      <c r="M36" s="255"/>
+      <c r="N36" s="256"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="28" t="s">
@@ -44614,13 +44629,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K37" s="261" t="str">
+      <c r="K37" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM3:FX52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L37" s="251"/>
-      <c r="M37" s="251"/>
-      <c r="N37" s="252"/>
+      <c r="L37" s="255"/>
+      <c r="M37" s="255"/>
+      <c r="N37" s="256"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
@@ -44662,13 +44677,13 @@
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K38" s="261" t="str">
+      <c r="K38" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY3:GJ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L38" s="251"/>
-      <c r="M38" s="251"/>
-      <c r="N38" s="252"/>
+      <c r="L38" s="255"/>
+      <c r="M38" s="255"/>
+      <c r="N38" s="256"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="28" t="s">
@@ -44710,13 +44725,13 @@
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K39" s="261" t="str">
+      <c r="K39" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK3:GW52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L39" s="251"/>
-      <c r="M39" s="251"/>
-      <c r="N39" s="252"/>
+      <c r="L39" s="255"/>
+      <c r="M39" s="255"/>
+      <c r="N39" s="256"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
@@ -44758,13 +44773,13 @@
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,11,0)</f>
         <v/>
       </c>
-      <c r="K40" s="261" t="str">
+      <c r="K40" s="254" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,12,0)</f>
         <v/>
       </c>
-      <c r="L40" s="251"/>
-      <c r="M40" s="251"/>
-      <c r="N40" s="252"/>
+      <c r="L40" s="255"/>
+      <c r="M40" s="255"/>
+      <c r="N40" s="256"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="21"/>
@@ -44788,20 +44803,20 @@
       </c>
       <c r="B42" s="36"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="262" t="s">
+      <c r="D42" s="252" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="262"/>
+      <c r="E42" s="252"/>
       <c r="F42" s="38"/>
       <c r="G42" s="39"/>
-      <c r="H42" s="263" t="s">
+      <c r="H42" s="253" t="s">
         <v>71</v>
       </c>
-      <c r="I42" s="263"/>
-      <c r="J42" s="263"/>
-      <c r="K42" s="263"/>
-      <c r="L42" s="263"/>
-      <c r="M42" s="263"/>
+      <c r="I42" s="253"/>
+      <c r="J42" s="253"/>
+      <c r="K42" s="253"/>
+      <c r="L42" s="253"/>
+      <c r="M42" s="253"/>
       <c r="N42" s="40"/>
       <c r="O42" s="16"/>
     </row>
@@ -44814,23 +44829,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="262" t="s">
+      <c r="D43" s="252" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="262"/>
+      <c r="E43" s="252"/>
       <c r="F43" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>2</v>
       </c>
       <c r="G43" s="39"/>
-      <c r="H43" s="263" t="s">
+      <c r="H43" s="253" t="s">
         <v>72</v>
       </c>
-      <c r="I43" s="263"/>
-      <c r="J43" s="263"/>
-      <c r="K43" s="263"/>
-      <c r="L43" s="263"/>
-      <c r="M43" s="263"/>
+      <c r="I43" s="253"/>
+      <c r="J43" s="253"/>
+      <c r="K43" s="253"/>
+      <c r="L43" s="253"/>
+      <c r="M43" s="253"/>
       <c r="N43" s="40"/>
       <c r="O43" s="16"/>
     </row>
@@ -44843,23 +44858,23 @@
         <v>3</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="262" t="s">
+      <c r="D44" s="252" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="262"/>
+      <c r="E44" s="252"/>
       <c r="F44" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>2</v>
       </c>
       <c r="G44" s="39"/>
-      <c r="H44" s="263" t="s">
+      <c r="H44" s="253" t="s">
         <v>73</v>
       </c>
-      <c r="I44" s="263"/>
-      <c r="J44" s="263"/>
-      <c r="K44" s="263"/>
-      <c r="L44" s="263"/>
-      <c r="M44" s="263"/>
+      <c r="I44" s="253"/>
+      <c r="J44" s="253"/>
+      <c r="K44" s="253"/>
+      <c r="L44" s="253"/>
+      <c r="M44" s="253"/>
       <c r="N44" s="40"/>
       <c r="O44" s="16"/>
     </row>
@@ -44872,23 +44887,23 @@
         <v>3</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="262" t="s">
+      <c r="D45" s="252" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="262"/>
+      <c r="E45" s="252"/>
       <c r="F45" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>4</v>
       </c>
       <c r="G45" s="39"/>
-      <c r="H45" s="263" t="s">
+      <c r="H45" s="253" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="263"/>
-      <c r="J45" s="263"/>
-      <c r="K45" s="263"/>
-      <c r="L45" s="263"/>
-      <c r="M45" s="263"/>
+      <c r="I45" s="253"/>
+      <c r="J45" s="253"/>
+      <c r="K45" s="253"/>
+      <c r="L45" s="253"/>
+      <c r="M45" s="253"/>
       <c r="N45" s="40"/>
       <c r="O45" s="16"/>
     </row>
@@ -44901,23 +44916,23 @@
         <v>1</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="262" t="s">
+      <c r="D46" s="252" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="262"/>
+      <c r="E46" s="252"/>
       <c r="F46" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>3</v>
       </c>
       <c r="G46" s="39"/>
-      <c r="H46" s="263" t="s">
+      <c r="H46" s="253" t="s">
         <v>75</v>
       </c>
-      <c r="I46" s="263"/>
-      <c r="J46" s="263"/>
-      <c r="K46" s="263"/>
-      <c r="L46" s="263"/>
-      <c r="M46" s="263"/>
+      <c r="I46" s="253"/>
+      <c r="J46" s="253"/>
+      <c r="K46" s="253"/>
+      <c r="L46" s="253"/>
+      <c r="M46" s="253"/>
       <c r="N46" s="40"/>
       <c r="O46" s="16"/>
     </row>
@@ -44930,23 +44945,23 @@
         <v>4</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="262" t="s">
+      <c r="D47" s="252" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="262"/>
+      <c r="E47" s="252"/>
       <c r="F47" s="38">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="39"/>
-      <c r="H47" s="263" t="s">
+      <c r="H47" s="253" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="263"/>
-      <c r="J47" s="263"/>
-      <c r="K47" s="263"/>
-      <c r="L47" s="263"/>
-      <c r="M47" s="263"/>
+      <c r="I47" s="253"/>
+      <c r="J47" s="253"/>
+      <c r="K47" s="253"/>
+      <c r="L47" s="253"/>
+      <c r="M47" s="253"/>
       <c r="N47" s="40"/>
       <c r="O47" s="16"/>
     </row>
@@ -45051,11 +45066,11 @@
       <c r="O52" s="16"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="264" t="s">
+      <c r="A53" s="239" t="s">
         <v>77</v>
       </c>
-      <c r="B53" s="265"/>
-      <c r="C53" s="265"/>
+      <c r="B53" s="240"/>
+      <c r="C53" s="240"/>
       <c r="D53" s="16" t="s">
         <v>78</v>
       </c>
@@ -45073,16 +45088,16 @@
       <c r="M53" s="16"/>
       <c r="N53" s="15"/>
       <c r="O53" s="16"/>
-      <c r="R53" s="267"/>
-      <c r="S53" s="267"/>
-      <c r="T53" s="267"/>
+      <c r="R53" s="241"/>
+      <c r="S53" s="241"/>
+      <c r="T53" s="241"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="264" t="s">
+      <c r="A54" s="239" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="265"/>
-      <c r="C54" s="265"/>
+      <c r="B54" s="240"/>
+      <c r="C54" s="240"/>
       <c r="D54" s="16" t="s">
         <v>78</v>
       </c>
@@ -45097,43 +45112,43 @@
       <c r="M54" s="16"/>
       <c r="N54" s="15"/>
       <c r="O54" s="16"/>
-      <c r="R54" s="267"/>
-      <c r="S54" s="267"/>
-      <c r="T54" s="267"/>
+      <c r="R54" s="241"/>
+      <c r="S54" s="241"/>
+      <c r="T54" s="241"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="264" t="s">
+      <c r="A55" s="239" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="265"/>
-      <c r="C55" s="265"/>
+      <c r="B55" s="240"/>
+      <c r="C55" s="240"/>
       <c r="D55" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="266" t="str">
+      <c r="E55" s="251" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="266"/>
-      <c r="G55" s="266"/>
-      <c r="H55" s="266"/>
-      <c r="I55" s="266"/>
-      <c r="J55" s="266"/>
+      <c r="F55" s="251"/>
+      <c r="G55" s="251"/>
+      <c r="H55" s="251"/>
+      <c r="I55" s="251"/>
+      <c r="J55" s="251"/>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
       <c r="N55" s="15"/>
       <c r="O55" s="16"/>
-      <c r="R55" s="267"/>
-      <c r="S55" s="267"/>
-      <c r="T55" s="267"/>
+      <c r="R55" s="241"/>
+      <c r="S55" s="241"/>
+      <c r="T55" s="241"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="264" t="s">
+      <c r="A56" s="239" t="s">
         <v>81</v>
       </c>
-      <c r="B56" s="265"/>
-      <c r="C56" s="265"/>
+      <c r="B56" s="240"/>
+      <c r="C56" s="240"/>
       <c r="D56" s="16" t="s">
         <v>78</v>
       </c>
@@ -45151,9 +45166,9 @@
       <c r="M56" s="16"/>
       <c r="N56" s="15"/>
       <c r="O56" s="16"/>
-      <c r="R56" s="267"/>
-      <c r="S56" s="267"/>
-      <c r="T56" s="267"/>
+      <c r="R56" s="241"/>
+      <c r="S56" s="241"/>
+      <c r="T56" s="241"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="23"/>
@@ -45190,6 +45205,65 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -45206,65 +45280,6 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>

--- a/Report JSS 1E.xlsx
+++ b/Report JSS 1E.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Comments" sheetId="4" r:id="rId1"/>
@@ -2125,23 +2125,29 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2158,26 +2164,67 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2206,50 +2253,6 @@
     <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2270,9 +2273,6 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Hyperlink" xfId="19" builtinId="8"/>
@@ -3543,7 +3543,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3634,7 +3634,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3730,7 +3730,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9190,14 +9190,14 @@
   <sheetData>
     <row r="1" spans="1:216">
       <c r="A1" s="41"/>
-      <c r="B1" s="233" t="s">
+      <c r="B1" s="223" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
       <c r="H1" s="49"/>
       <c r="I1" s="49"/>
       <c r="J1" s="50"/>
@@ -9206,28 +9206,28 @@
       <c r="M1" s="41"/>
       <c r="N1" s="56"/>
       <c r="O1" s="55"/>
-      <c r="P1" s="237" t="s">
+      <c r="P1" s="228" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="238"/>
-      <c r="R1" s="238"/>
-      <c r="S1" s="238"/>
-      <c r="T1" s="238"/>
-      <c r="U1" s="238"/>
-      <c r="V1" s="238"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="229"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
       <c r="W1" s="57"/>
       <c r="X1" s="57"/>
       <c r="Y1" s="54"/>
       <c r="Z1" s="79"/>
-      <c r="AA1" s="227" t="s">
+      <c r="AA1" s="224" t="s">
         <v>103</v>
       </c>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="227"/>
-      <c r="AE1" s="227"/>
-      <c r="AF1" s="227"/>
-      <c r="AG1" s="227"/>
+      <c r="AB1" s="224"/>
+      <c r="AC1" s="224"/>
+      <c r="AD1" s="224"/>
+      <c r="AE1" s="224"/>
+      <c r="AF1" s="224"/>
+      <c r="AG1" s="224"/>
       <c r="AH1" s="79"/>
       <c r="AI1" s="79"/>
       <c r="AJ1" s="79"/>
@@ -9247,197 +9247,197 @@
       <c r="AV1" s="44"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="85"/>
-      <c r="AY1" s="234" t="s">
+      <c r="AY1" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="AZ1" s="234"/>
-      <c r="BA1" s="234"/>
-      <c r="BB1" s="234"/>
-      <c r="BC1" s="234"/>
-      <c r="BD1" s="234"/>
-      <c r="BE1" s="234"/>
+      <c r="AZ1" s="225"/>
+      <c r="BA1" s="225"/>
+      <c r="BB1" s="225"/>
+      <c r="BC1" s="225"/>
+      <c r="BD1" s="225"/>
+      <c r="BE1" s="225"/>
       <c r="BF1" s="85"/>
       <c r="BG1" s="85"/>
       <c r="BH1" s="85"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="90"/>
-      <c r="BK1" s="235" t="s">
+      <c r="BK1" s="226" t="s">
         <v>63</v>
       </c>
-      <c r="BL1" s="236"/>
-      <c r="BM1" s="236"/>
-      <c r="BN1" s="236"/>
-      <c r="BO1" s="236"/>
-      <c r="BP1" s="236"/>
-      <c r="BQ1" s="236"/>
+      <c r="BL1" s="227"/>
+      <c r="BM1" s="227"/>
+      <c r="BN1" s="227"/>
+      <c r="BO1" s="227"/>
+      <c r="BP1" s="227"/>
+      <c r="BQ1" s="227"/>
       <c r="BR1" s="90"/>
       <c r="BS1" s="90"/>
       <c r="BT1" s="90"/>
       <c r="BU1" s="3"/>
       <c r="BV1" s="95"/>
-      <c r="BW1" s="228" t="s">
+      <c r="BW1" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="BX1" s="228"/>
-      <c r="BY1" s="228"/>
-      <c r="BZ1" s="228"/>
-      <c r="CA1" s="228"/>
-      <c r="CB1" s="228"/>
-      <c r="CC1" s="228"/>
+      <c r="BX1" s="230"/>
+      <c r="BY1" s="230"/>
+      <c r="BZ1" s="230"/>
+      <c r="CA1" s="230"/>
+      <c r="CB1" s="230"/>
+      <c r="CC1" s="230"/>
       <c r="CD1" s="95"/>
       <c r="CE1" s="95"/>
       <c r="CF1" s="95"/>
       <c r="CG1" s="3"/>
       <c r="CH1" s="64"/>
-      <c r="CI1" s="229" t="s">
+      <c r="CI1" s="231" t="s">
         <v>87</v>
       </c>
-      <c r="CJ1" s="229"/>
-      <c r="CK1" s="229"/>
-      <c r="CL1" s="229"/>
-      <c r="CM1" s="229"/>
-      <c r="CN1" s="229"/>
-      <c r="CO1" s="229"/>
+      <c r="CJ1" s="231"/>
+      <c r="CK1" s="231"/>
+      <c r="CL1" s="231"/>
+      <c r="CM1" s="231"/>
+      <c r="CN1" s="231"/>
+      <c r="CO1" s="231"/>
       <c r="CP1" s="64"/>
       <c r="CQ1" s="64"/>
       <c r="CR1" s="64"/>
       <c r="CS1" s="3"/>
       <c r="CT1" s="69"/>
-      <c r="CU1" s="230" t="s">
+      <c r="CU1" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="CV1" s="230"/>
-      <c r="CW1" s="230"/>
-      <c r="CX1" s="230"/>
-      <c r="CY1" s="230"/>
-      <c r="CZ1" s="230"/>
-      <c r="DA1" s="230"/>
+      <c r="CV1" s="232"/>
+      <c r="CW1" s="232"/>
+      <c r="CX1" s="232"/>
+      <c r="CY1" s="232"/>
+      <c r="CZ1" s="232"/>
+      <c r="DA1" s="232"/>
       <c r="DB1" s="69"/>
       <c r="DC1" s="69"/>
       <c r="DD1" s="69"/>
       <c r="DE1" s="3"/>
       <c r="DF1" s="56"/>
-      <c r="DG1" s="231" t="s">
+      <c r="DG1" s="233" t="s">
         <v>88</v>
       </c>
-      <c r="DH1" s="231"/>
-      <c r="DI1" s="231"/>
-      <c r="DJ1" s="231"/>
-      <c r="DK1" s="231"/>
-      <c r="DL1" s="231"/>
-      <c r="DM1" s="231"/>
+      <c r="DH1" s="233"/>
+      <c r="DI1" s="233"/>
+      <c r="DJ1" s="233"/>
+      <c r="DK1" s="233"/>
+      <c r="DL1" s="233"/>
+      <c r="DM1" s="233"/>
       <c r="DN1" s="56"/>
       <c r="DO1" s="56"/>
       <c r="DP1" s="56"/>
       <c r="DQ1" s="3"/>
       <c r="DR1" s="105"/>
-      <c r="DS1" s="232" t="s">
+      <c r="DS1" s="234" t="s">
         <v>89</v>
       </c>
-      <c r="DT1" s="232"/>
-      <c r="DU1" s="232"/>
-      <c r="DV1" s="232"/>
-      <c r="DW1" s="232"/>
-      <c r="DX1" s="232"/>
-      <c r="DY1" s="232"/>
+      <c r="DT1" s="234"/>
+      <c r="DU1" s="234"/>
+      <c r="DV1" s="234"/>
+      <c r="DW1" s="234"/>
+      <c r="DX1" s="234"/>
+      <c r="DY1" s="234"/>
       <c r="DZ1" s="105"/>
       <c r="EA1" s="105"/>
       <c r="EB1" s="105"/>
       <c r="EC1" s="3"/>
       <c r="ED1" s="74"/>
-      <c r="EE1" s="224" t="s">
+      <c r="EE1" s="237" t="s">
         <v>64</v>
       </c>
-      <c r="EF1" s="224"/>
-      <c r="EG1" s="224"/>
-      <c r="EH1" s="224"/>
-      <c r="EI1" s="224"/>
-      <c r="EJ1" s="224"/>
-      <c r="EK1" s="224"/>
+      <c r="EF1" s="237"/>
+      <c r="EG1" s="237"/>
+      <c r="EH1" s="237"/>
+      <c r="EI1" s="237"/>
+      <c r="EJ1" s="237"/>
+      <c r="EK1" s="237"/>
       <c r="EL1" s="74"/>
       <c r="EM1" s="74"/>
       <c r="EN1" s="74"/>
       <c r="EO1" s="3"/>
       <c r="EP1" s="100"/>
-      <c r="EQ1" s="225" t="s">
+      <c r="EQ1" s="238" t="s">
         <v>67</v>
       </c>
-      <c r="ER1" s="225"/>
-      <c r="ES1" s="225"/>
-      <c r="ET1" s="225"/>
-      <c r="EU1" s="225"/>
-      <c r="EV1" s="225"/>
-      <c r="EW1" s="225"/>
+      <c r="ER1" s="238"/>
+      <c r="ES1" s="238"/>
+      <c r="ET1" s="238"/>
+      <c r="EU1" s="238"/>
+      <c r="EV1" s="238"/>
+      <c r="EW1" s="238"/>
       <c r="EX1" s="100"/>
       <c r="EY1" s="100"/>
       <c r="EZ1" s="100"/>
       <c r="FA1" s="3"/>
       <c r="FB1" s="116"/>
-      <c r="FC1" s="223" t="s">
+      <c r="FC1" s="236" t="s">
         <v>65</v>
       </c>
-      <c r="FD1" s="223"/>
-      <c r="FE1" s="223"/>
-      <c r="FF1" s="223"/>
-      <c r="FG1" s="223"/>
-      <c r="FH1" s="223"/>
-      <c r="FI1" s="223"/>
+      <c r="FD1" s="236"/>
+      <c r="FE1" s="236"/>
+      <c r="FF1" s="236"/>
+      <c r="FG1" s="236"/>
+      <c r="FH1" s="236"/>
+      <c r="FI1" s="236"/>
       <c r="FJ1" s="116"/>
       <c r="FK1" s="116"/>
       <c r="FL1" s="116"/>
       <c r="FM1" s="3"/>
       <c r="FN1" s="50"/>
-      <c r="FO1" s="226" t="s">
+      <c r="FO1" s="239" t="s">
         <v>93</v>
       </c>
-      <c r="FP1" s="226"/>
-      <c r="FQ1" s="226"/>
-      <c r="FR1" s="226"/>
-      <c r="FS1" s="226"/>
-      <c r="FT1" s="226"/>
-      <c r="FU1" s="226"/>
+      <c r="FP1" s="239"/>
+      <c r="FQ1" s="239"/>
+      <c r="FR1" s="239"/>
+      <c r="FS1" s="239"/>
+      <c r="FT1" s="239"/>
+      <c r="FU1" s="239"/>
       <c r="FV1" s="50"/>
       <c r="FW1" s="50"/>
       <c r="FX1" s="50"/>
       <c r="FY1" s="3"/>
       <c r="FZ1" s="79"/>
-      <c r="GA1" s="227" t="s">
+      <c r="GA1" s="224" t="s">
         <v>94</v>
       </c>
-      <c r="GB1" s="227"/>
-      <c r="GC1" s="227"/>
-      <c r="GD1" s="227"/>
-      <c r="GE1" s="227"/>
-      <c r="GF1" s="227"/>
-      <c r="GG1" s="227"/>
+      <c r="GB1" s="224"/>
+      <c r="GC1" s="224"/>
+      <c r="GD1" s="224"/>
+      <c r="GE1" s="224"/>
+      <c r="GF1" s="224"/>
+      <c r="GG1" s="224"/>
       <c r="GH1" s="79"/>
       <c r="GI1" s="79"/>
       <c r="GJ1" s="79"/>
       <c r="GK1" s="3"/>
       <c r="GL1" s="116"/>
-      <c r="GM1" s="223" t="s">
+      <c r="GM1" s="236" t="s">
         <v>62</v>
       </c>
-      <c r="GN1" s="223"/>
-      <c r="GO1" s="223"/>
-      <c r="GP1" s="223"/>
-      <c r="GQ1" s="223"/>
-      <c r="GR1" s="223"/>
-      <c r="GS1" s="223"/>
+      <c r="GN1" s="236"/>
+      <c r="GO1" s="236"/>
+      <c r="GP1" s="236"/>
+      <c r="GQ1" s="236"/>
+      <c r="GR1" s="236"/>
+      <c r="GS1" s="236"/>
       <c r="GT1" s="116"/>
       <c r="GU1" s="116"/>
       <c r="GV1" s="116"/>
       <c r="GW1" s="3"/>
       <c r="GX1" s="110"/>
-      <c r="GY1" s="222" t="s">
+      <c r="GY1" s="235" t="s">
         <v>82</v>
       </c>
-      <c r="GZ1" s="222"/>
-      <c r="HA1" s="222"/>
-      <c r="HB1" s="222"/>
-      <c r="HC1" s="222"/>
-      <c r="HD1" s="222"/>
-      <c r="HE1" s="222"/>
+      <c r="GZ1" s="235"/>
+      <c r="HA1" s="235"/>
+      <c r="HB1" s="235"/>
+      <c r="HC1" s="235"/>
+      <c r="HD1" s="235"/>
+      <c r="HE1" s="235"/>
       <c r="HF1" s="110"/>
       <c r="HG1" s="110"/>
       <c r="HH1" s="110"/>
@@ -37742,7 +37742,7 @@
       <c r="A43" s="183">
         <v>41</v>
       </c>
-      <c r="B43" s="285" t="s">
+      <c r="B43" s="222" t="s">
         <v>229</v>
       </c>
       <c r="C43" s="130">
@@ -39122,7 +39122,7 @@
       <c r="A45" s="183">
         <v>43</v>
       </c>
-      <c r="B45" s="285" t="s">
+      <c r="B45" s="222" t="s">
         <v>208</v>
       </c>
       <c r="C45" s="144">
@@ -43425,16 +43425,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AY1:BE1"/>
-    <mergeCell ref="BK1:BQ1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="BW1:CC1"/>
-    <mergeCell ref="CI1:CO1"/>
-    <mergeCell ref="CU1:DA1"/>
-    <mergeCell ref="DG1:DM1"/>
-    <mergeCell ref="DS1:DY1"/>
     <mergeCell ref="GY1:HE1"/>
     <mergeCell ref="GM1:GS1"/>
     <mergeCell ref="EE1:EK1"/>
@@ -43442,6 +43432,16 @@
     <mergeCell ref="FC1:FI1"/>
     <mergeCell ref="FO1:FU1"/>
     <mergeCell ref="GA1:GG1"/>
+    <mergeCell ref="BW1:CC1"/>
+    <mergeCell ref="CI1:CO1"/>
+    <mergeCell ref="CU1:DA1"/>
+    <mergeCell ref="DG1:DM1"/>
+    <mergeCell ref="DS1:DY1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AY1:BE1"/>
+    <mergeCell ref="BK1:BQ1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43603,114 +43603,114 @@
       <c r="A10" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="273" t="str">
+      <c r="B10" s="240" t="str">
         <f>VLOOKUP(B14,Data!A1:I53,2,0)</f>
         <v>AKILAHYEL SUCCESS GWANDI</v>
       </c>
-      <c r="C10" s="273"/>
-      <c r="D10" s="273"/>
-      <c r="E10" s="273"/>
-      <c r="F10" s="273"/>
-      <c r="G10" s="273"/>
+      <c r="C10" s="240"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="240"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
-      <c r="K10" s="271" t="s">
+      <c r="K10" s="241" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="271"/>
-      <c r="M10" s="273" t="str">
+      <c r="L10" s="241"/>
+      <c r="M10" s="240" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,7,0)</f>
         <v xml:space="preserve">1st </v>
       </c>
-      <c r="N10" s="274"/>
+      <c r="N10" s="242"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="271">
+      <c r="B11" s="241">
         <f>VLOOKUP(B14,Data!A2:H53,4,0)</f>
         <v>10</v>
       </c>
-      <c r="C11" s="271"/>
-      <c r="D11" s="271"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="271"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
       <c r="H11" s="29"/>
       <c r="I11" s="29"/>
       <c r="J11" s="29"/>
-      <c r="K11" s="271" t="s">
+      <c r="K11" s="241" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="271"/>
-      <c r="M11" s="273" t="str">
+      <c r="L11" s="241"/>
+      <c r="M11" s="240" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,3,0)</f>
         <v>JSS 1 E</v>
       </c>
-      <c r="N11" s="274"/>
+      <c r="N11" s="242"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="273" t="str">
+      <c r="B12" s="240" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,5,0)</f>
         <v>BORNO</v>
       </c>
-      <c r="C12" s="273"/>
-      <c r="D12" s="273"/>
-      <c r="E12" s="273"/>
-      <c r="F12" s="273"/>
-      <c r="G12" s="273"/>
+      <c r="C12" s="240"/>
+      <c r="D12" s="240"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="240"/>
+      <c r="G12" s="240"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
-      <c r="K12" s="271" t="s">
+      <c r="K12" s="241" t="s">
         <v>41</v>
       </c>
-      <c r="L12" s="271"/>
-      <c r="M12" s="273" t="str">
+      <c r="L12" s="241"/>
+      <c r="M12" s="240" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,8,0)</f>
         <v>16th January, 2026</v>
       </c>
-      <c r="N12" s="274"/>
+      <c r="N12" s="242"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="273" t="str">
+      <c r="B13" s="240" t="str">
         <f>VLOOKUP(B14,Data!A2:H53,6,0)</f>
         <v>HAWUL</v>
       </c>
-      <c r="C13" s="273"/>
-      <c r="D13" s="273"/>
-      <c r="E13" s="273"/>
-      <c r="F13" s="273"/>
-      <c r="G13" s="273"/>
+      <c r="C13" s="240"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="240"/>
+      <c r="F13" s="240"/>
+      <c r="G13" s="240"/>
       <c r="H13" s="29"/>
       <c r="I13" s="29"/>
       <c r="J13" s="29"/>
-      <c r="K13" s="271" t="s">
+      <c r="K13" s="241" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="271"/>
-      <c r="M13" s="273" t="str">
+      <c r="L13" s="241"/>
+      <c r="M13" s="240" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="274"/>
+      <c r="N13" s="242"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="271">
+      <c r="B14" s="241">
         <v>24</v>
       </c>
-      <c r="C14" s="271"/>
+      <c r="C14" s="241"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
@@ -43718,10 +43718,10 @@
       <c r="H14" s="29"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
-      <c r="K14" s="272"/>
-      <c r="L14" s="272"/>
-      <c r="M14" s="273"/>
-      <c r="N14" s="274"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="240"/>
+      <c r="N14" s="242"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="34" t="s">
@@ -43739,10 +43739,10 @@
       <c r="H15" s="29"/>
       <c r="I15" s="29"/>
       <c r="J15" s="29"/>
-      <c r="K15" s="275"/>
-      <c r="L15" s="275"/>
-      <c r="M15" s="272"/>
-      <c r="N15" s="276"/>
+      <c r="K15" s="244"/>
+      <c r="L15" s="244"/>
+      <c r="M15" s="243"/>
+      <c r="N15" s="245"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="34" t="s">
@@ -43782,111 +43782,111 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="242" t="s">
+      <c r="A18" s="269" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="244" t="s">
+      <c r="B18" s="271" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="271" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="244" t="s">
+      <c r="D18" s="271" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="244" t="s">
+      <c r="E18" s="271" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="246" t="s">
+      <c r="F18" s="273" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="244" t="s">
+      <c r="G18" s="271" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="244" t="s">
+      <c r="H18" s="271" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="246" t="s">
+      <c r="I18" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="248" t="s">
+      <c r="J18" s="275" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="263" t="s">
+      <c r="K18" s="246" t="s">
         <v>53</v>
       </c>
-      <c r="L18" s="264"/>
-      <c r="M18" s="265">
+      <c r="L18" s="247"/>
+      <c r="M18" s="248">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="266"/>
+      <c r="N18" s="249"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="243"/>
-      <c r="B19" s="245"/>
-      <c r="C19" s="245"/>
-      <c r="D19" s="245"/>
-      <c r="E19" s="245"/>
-      <c r="F19" s="247"/>
-      <c r="G19" s="245"/>
-      <c r="H19" s="245"/>
-      <c r="I19" s="247"/>
-      <c r="J19" s="249"/>
-      <c r="K19" s="267" t="s">
+      <c r="A19" s="270"/>
+      <c r="B19" s="272"/>
+      <c r="C19" s="272"/>
+      <c r="D19" s="272"/>
+      <c r="E19" s="272"/>
+      <c r="F19" s="274"/>
+      <c r="G19" s="272"/>
+      <c r="H19" s="272"/>
+      <c r="I19" s="274"/>
+      <c r="J19" s="276"/>
+      <c r="K19" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="L19" s="268"/>
-      <c r="M19" s="255">
+      <c r="L19" s="251"/>
+      <c r="M19" s="252">
         <f>SUM(H23:H40)</f>
         <v>1161</v>
       </c>
-      <c r="N19" s="256"/>
+      <c r="N19" s="253"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="243"/>
-      <c r="B20" s="245"/>
-      <c r="C20" s="245"/>
-      <c r="D20" s="245"/>
-      <c r="E20" s="245"/>
-      <c r="F20" s="247"/>
-      <c r="G20" s="245"/>
-      <c r="H20" s="245"/>
-      <c r="I20" s="247"/>
-      <c r="J20" s="249"/>
-      <c r="K20" s="267" t="s">
+      <c r="A20" s="270"/>
+      <c r="B20" s="272"/>
+      <c r="C20" s="272"/>
+      <c r="D20" s="272"/>
+      <c r="E20" s="272"/>
+      <c r="F20" s="274"/>
+      <c r="G20" s="272"/>
+      <c r="H20" s="272"/>
+      <c r="I20" s="274"/>
+      <c r="J20" s="276"/>
+      <c r="K20" s="250" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="268"/>
-      <c r="M20" s="269">
+      <c r="L20" s="251"/>
+      <c r="M20" s="254">
         <f>VLOOKUP(B14,Bsheet!A2:V51,21,0)</f>
         <v>69</v>
       </c>
-      <c r="N20" s="270"/>
+      <c r="N20" s="255"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="243"/>
-      <c r="B21" s="245"/>
-      <c r="C21" s="245"/>
-      <c r="D21" s="245"/>
-      <c r="E21" s="245"/>
-      <c r="F21" s="247"/>
-      <c r="G21" s="245"/>
-      <c r="H21" s="245"/>
-      <c r="I21" s="247"/>
-      <c r="J21" s="250"/>
-      <c r="K21" s="257" t="s">
+      <c r="A21" s="270"/>
+      <c r="B21" s="272"/>
+      <c r="C21" s="272"/>
+      <c r="D21" s="272"/>
+      <c r="E21" s="272"/>
+      <c r="F21" s="274"/>
+      <c r="G21" s="272"/>
+      <c r="H21" s="272"/>
+      <c r="I21" s="274"/>
+      <c r="J21" s="277"/>
+      <c r="K21" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="258"/>
-      <c r="M21" s="259">
+      <c r="L21" s="257"/>
+      <c r="M21" s="258">
         <f>VLOOKUP(B14,Bsheet!A2:V51,22,0)</f>
         <v>10</v>
       </c>
-      <c r="N21" s="260"/>
+      <c r="N21" s="259"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="243"/>
+      <c r="A22" s="270"/>
       <c r="B22" s="27" t="s">
         <v>57</v>
       </c>
@@ -43910,12 +43910,12 @@
       </c>
       <c r="I22" s="124"/>
       <c r="J22" s="125"/>
-      <c r="K22" s="261" t="s">
+      <c r="K22" s="260" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="261"/>
-      <c r="M22" s="261"/>
-      <c r="N22" s="262"/>
+      <c r="L22" s="260"/>
+      <c r="M22" s="260"/>
+      <c r="N22" s="261"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="28" t="s">
@@ -43957,13 +43957,13 @@
         <f>VLOOKUP(B14,Scoresheet!A3:K52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K23" s="254" t="str">
+      <c r="K23" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L23" s="255"/>
-      <c r="M23" s="255"/>
-      <c r="N23" s="256"/>
+      <c r="L23" s="252"/>
+      <c r="M23" s="252"/>
+      <c r="N23" s="253"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="28" t="s">
@@ -44005,13 +44005,13 @@
         <f>VLOOKUP(B14,Scoresheet!M3:W52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K24" s="254" t="str">
+      <c r="K24" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!M3:X52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L24" s="255"/>
-      <c r="M24" s="255"/>
-      <c r="N24" s="256"/>
+      <c r="L24" s="252"/>
+      <c r="M24" s="252"/>
+      <c r="N24" s="253"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="28" t="s">
@@ -44053,13 +44053,13 @@
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K25" s="254" t="str">
+      <c r="K25" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y3:AJ52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L25" s="255"/>
-      <c r="M25" s="255"/>
-      <c r="N25" s="256"/>
+      <c r="L25" s="252"/>
+      <c r="M25" s="252"/>
+      <c r="N25" s="253"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="28" t="s">
@@ -44101,13 +44101,13 @@
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="254" t="str">
+      <c r="K26" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK3:AV52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L26" s="255"/>
-      <c r="M26" s="255"/>
-      <c r="N26" s="256"/>
+      <c r="L26" s="252"/>
+      <c r="M26" s="252"/>
+      <c r="N26" s="253"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="28" t="s">
@@ -44149,13 +44149,13 @@
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K27" s="254" t="str">
+      <c r="K27" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW3:BH52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L27" s="255"/>
-      <c r="M27" s="255"/>
-      <c r="N27" s="256"/>
+      <c r="L27" s="252"/>
+      <c r="M27" s="252"/>
+      <c r="N27" s="253"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="28" t="s">
@@ -44197,13 +44197,13 @@
         <f>VLOOKUP(B14,Scoresheet!BI3:BU52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K28" s="254" t="str">
+      <c r="K28" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI3:BT52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L28" s="255"/>
-      <c r="M28" s="255"/>
-      <c r="N28" s="256"/>
+      <c r="L28" s="252"/>
+      <c r="M28" s="252"/>
+      <c r="N28" s="253"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="28" t="s">
@@ -44245,13 +44245,13 @@
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K29" s="254" t="str">
+      <c r="K29" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU3:CF52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L29" s="255"/>
-      <c r="M29" s="255"/>
-      <c r="N29" s="256"/>
+      <c r="L29" s="252"/>
+      <c r="M29" s="252"/>
+      <c r="N29" s="253"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="28" t="s">
@@ -44293,13 +44293,13 @@
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K30" s="254" t="str">
+      <c r="K30" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG3:CR52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L30" s="255"/>
-      <c r="M30" s="255"/>
-      <c r="N30" s="256"/>
+      <c r="L30" s="252"/>
+      <c r="M30" s="252"/>
+      <c r="N30" s="253"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="28" t="s">
@@ -44341,13 +44341,13 @@
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K31" s="254" t="str">
+      <c r="K31" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS3:DD52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L31" s="255"/>
-      <c r="M31" s="255"/>
-      <c r="N31" s="256"/>
+      <c r="L31" s="252"/>
+      <c r="M31" s="252"/>
+      <c r="N31" s="253"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="28" t="s">
@@ -44389,13 +44389,13 @@
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K32" s="254" t="str">
+      <c r="K32" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE3:DP52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L32" s="255"/>
-      <c r="M32" s="255"/>
-      <c r="N32" s="256"/>
+      <c r="L32" s="252"/>
+      <c r="M32" s="252"/>
+      <c r="N32" s="253"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="28" t="s">
@@ -44437,13 +44437,13 @@
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K33" s="254" t="str">
+      <c r="K33" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EB52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L33" s="255"/>
-      <c r="M33" s="255"/>
-      <c r="N33" s="256"/>
+      <c r="L33" s="252"/>
+      <c r="M33" s="252"/>
+      <c r="N33" s="253"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="28" t="s">
@@ -44485,13 +44485,13 @@
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K34" s="254" t="str">
+      <c r="K34" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC3:EN52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L34" s="255"/>
-      <c r="M34" s="255"/>
-      <c r="N34" s="256"/>
+      <c r="L34" s="252"/>
+      <c r="M34" s="252"/>
+      <c r="N34" s="253"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="28" t="s">
@@ -44533,13 +44533,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K35" s="254" t="str">
+      <c r="K35" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EZ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L35" s="255"/>
-      <c r="M35" s="255"/>
-      <c r="N35" s="256"/>
+      <c r="L35" s="252"/>
+      <c r="M35" s="252"/>
+      <c r="N35" s="253"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="28" t="s">
@@ -44581,13 +44581,13 @@
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,11,0)</f>
         <v>P</v>
       </c>
-      <c r="K36" s="254" t="str">
+      <c r="K36" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA3:FL52,12,0)</f>
         <v>Pass</v>
       </c>
-      <c r="L36" s="255"/>
-      <c r="M36" s="255"/>
-      <c r="N36" s="256"/>
+      <c r="L36" s="252"/>
+      <c r="M36" s="252"/>
+      <c r="N36" s="253"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="28" t="s">
@@ -44629,13 +44629,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K37" s="254" t="str">
+      <c r="K37" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM3:FX52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L37" s="255"/>
-      <c r="M37" s="255"/>
-      <c r="N37" s="256"/>
+      <c r="L37" s="252"/>
+      <c r="M37" s="252"/>
+      <c r="N37" s="253"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="28" t="s">
@@ -44677,13 +44677,13 @@
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K38" s="254" t="str">
+      <c r="K38" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY3:GJ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L38" s="255"/>
-      <c r="M38" s="255"/>
-      <c r="N38" s="256"/>
+      <c r="L38" s="252"/>
+      <c r="M38" s="252"/>
+      <c r="N38" s="253"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="28" t="s">
@@ -44725,13 +44725,13 @@
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K39" s="254" t="str">
+      <c r="K39" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK3:GW52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L39" s="255"/>
-      <c r="M39" s="255"/>
-      <c r="N39" s="256"/>
+      <c r="L39" s="252"/>
+      <c r="M39" s="252"/>
+      <c r="N39" s="253"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="28" t="s">
@@ -44773,13 +44773,13 @@
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,11,0)</f>
         <v/>
       </c>
-      <c r="K40" s="254" t="str">
+      <c r="K40" s="262" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,12,0)</f>
         <v/>
       </c>
-      <c r="L40" s="255"/>
-      <c r="M40" s="255"/>
-      <c r="N40" s="256"/>
+      <c r="L40" s="252"/>
+      <c r="M40" s="252"/>
+      <c r="N40" s="253"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="21"/>
@@ -44803,20 +44803,20 @@
       </c>
       <c r="B42" s="36"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="252" t="s">
+      <c r="D42" s="263" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="252"/>
+      <c r="E42" s="263"/>
       <c r="F42" s="38"/>
       <c r="G42" s="39"/>
-      <c r="H42" s="253" t="s">
+      <c r="H42" s="264" t="s">
         <v>71</v>
       </c>
-      <c r="I42" s="253"/>
-      <c r="J42" s="253"/>
-      <c r="K42" s="253"/>
-      <c r="L42" s="253"/>
-      <c r="M42" s="253"/>
+      <c r="I42" s="264"/>
+      <c r="J42" s="264"/>
+      <c r="K42" s="264"/>
+      <c r="L42" s="264"/>
+      <c r="M42" s="264"/>
       <c r="N42" s="40"/>
       <c r="O42" s="16"/>
     </row>
@@ -44829,23 +44829,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="252" t="s">
+      <c r="D43" s="263" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="252"/>
+      <c r="E43" s="263"/>
       <c r="F43" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>2</v>
       </c>
       <c r="G43" s="39"/>
-      <c r="H43" s="253" t="s">
+      <c r="H43" s="264" t="s">
         <v>72</v>
       </c>
-      <c r="I43" s="253"/>
-      <c r="J43" s="253"/>
-      <c r="K43" s="253"/>
-      <c r="L43" s="253"/>
-      <c r="M43" s="253"/>
+      <c r="I43" s="264"/>
+      <c r="J43" s="264"/>
+      <c r="K43" s="264"/>
+      <c r="L43" s="264"/>
+      <c r="M43" s="264"/>
       <c r="N43" s="40"/>
       <c r="O43" s="16"/>
     </row>
@@ -44858,23 +44858,23 @@
         <v>3</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="252" t="s">
+      <c r="D44" s="263" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="252"/>
+      <c r="E44" s="263"/>
       <c r="F44" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>2</v>
       </c>
       <c r="G44" s="39"/>
-      <c r="H44" s="253" t="s">
+      <c r="H44" s="264" t="s">
         <v>73</v>
       </c>
-      <c r="I44" s="253"/>
-      <c r="J44" s="253"/>
-      <c r="K44" s="253"/>
-      <c r="L44" s="253"/>
-      <c r="M44" s="253"/>
+      <c r="I44" s="264"/>
+      <c r="J44" s="264"/>
+      <c r="K44" s="264"/>
+      <c r="L44" s="264"/>
+      <c r="M44" s="264"/>
       <c r="N44" s="40"/>
       <c r="O44" s="16"/>
     </row>
@@ -44887,23 +44887,23 @@
         <v>3</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="252" t="s">
+      <c r="D45" s="263" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="252"/>
+      <c r="E45" s="263"/>
       <c r="F45" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>4</v>
       </c>
       <c r="G45" s="39"/>
-      <c r="H45" s="253" t="s">
+      <c r="H45" s="264" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="253"/>
-      <c r="J45" s="253"/>
-      <c r="K45" s="253"/>
-      <c r="L45" s="253"/>
-      <c r="M45" s="253"/>
+      <c r="I45" s="264"/>
+      <c r="J45" s="264"/>
+      <c r="K45" s="264"/>
+      <c r="L45" s="264"/>
+      <c r="M45" s="264"/>
       <c r="N45" s="40"/>
       <c r="O45" s="16"/>
     </row>
@@ -44916,23 +44916,23 @@
         <v>1</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="252" t="s">
+      <c r="D46" s="263" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="252"/>
+      <c r="E46" s="263"/>
       <c r="F46" s="38">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>3</v>
       </c>
       <c r="G46" s="39"/>
-      <c r="H46" s="253" t="s">
+      <c r="H46" s="264" t="s">
         <v>75</v>
       </c>
-      <c r="I46" s="253"/>
-      <c r="J46" s="253"/>
-      <c r="K46" s="253"/>
-      <c r="L46" s="253"/>
-      <c r="M46" s="253"/>
+      <c r="I46" s="264"/>
+      <c r="J46" s="264"/>
+      <c r="K46" s="264"/>
+      <c r="L46" s="264"/>
+      <c r="M46" s="264"/>
       <c r="N46" s="40"/>
       <c r="O46" s="16"/>
     </row>
@@ -44945,23 +44945,23 @@
         <v>4</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="252" t="s">
+      <c r="D47" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="252"/>
+      <c r="E47" s="263"/>
       <c r="F47" s="38">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="39"/>
-      <c r="H47" s="253" t="s">
+      <c r="H47" s="264" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="253"/>
-      <c r="J47" s="253"/>
-      <c r="K47" s="253"/>
-      <c r="L47" s="253"/>
-      <c r="M47" s="253"/>
+      <c r="I47" s="264"/>
+      <c r="J47" s="264"/>
+      <c r="K47" s="264"/>
+      <c r="L47" s="264"/>
+      <c r="M47" s="264"/>
       <c r="N47" s="40"/>
       <c r="O47" s="16"/>
     </row>
@@ -45066,11 +45066,11 @@
       <c r="O52" s="16"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="239" t="s">
+      <c r="A53" s="265" t="s">
         <v>77</v>
       </c>
-      <c r="B53" s="240"/>
-      <c r="C53" s="240"/>
+      <c r="B53" s="266"/>
+      <c r="C53" s="266"/>
       <c r="D53" s="16" t="s">
         <v>78</v>
       </c>
@@ -45088,16 +45088,16 @@
       <c r="M53" s="16"/>
       <c r="N53" s="15"/>
       <c r="O53" s="16"/>
-      <c r="R53" s="241"/>
-      <c r="S53" s="241"/>
-      <c r="T53" s="241"/>
+      <c r="R53" s="268"/>
+      <c r="S53" s="268"/>
+      <c r="T53" s="268"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="239" t="s">
+      <c r="A54" s="265" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="240"/>
-      <c r="C54" s="240"/>
+      <c r="B54" s="266"/>
+      <c r="C54" s="266"/>
       <c r="D54" s="16" t="s">
         <v>78</v>
       </c>
@@ -45112,43 +45112,43 @@
       <c r="M54" s="16"/>
       <c r="N54" s="15"/>
       <c r="O54" s="16"/>
-      <c r="R54" s="241"/>
-      <c r="S54" s="241"/>
-      <c r="T54" s="241"/>
+      <c r="R54" s="268"/>
+      <c r="S54" s="268"/>
+      <c r="T54" s="268"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="239" t="s">
+      <c r="A55" s="265" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="240"/>
-      <c r="C55" s="240"/>
+      <c r="B55" s="266"/>
+      <c r="C55" s="266"/>
       <c r="D55" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="251" t="str">
+      <c r="E55" s="267" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="251"/>
-      <c r="G55" s="251"/>
-      <c r="H55" s="251"/>
-      <c r="I55" s="251"/>
-      <c r="J55" s="251"/>
+      <c r="F55" s="267"/>
+      <c r="G55" s="267"/>
+      <c r="H55" s="267"/>
+      <c r="I55" s="267"/>
+      <c r="J55" s="267"/>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
       <c r="N55" s="15"/>
       <c r="O55" s="16"/>
-      <c r="R55" s="241"/>
-      <c r="S55" s="241"/>
-      <c r="T55" s="241"/>
+      <c r="R55" s="268"/>
+      <c r="S55" s="268"/>
+      <c r="T55" s="268"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="239" t="s">
+      <c r="A56" s="265" t="s">
         <v>81</v>
       </c>
-      <c r="B56" s="240"/>
-      <c r="C56" s="240"/>
+      <c r="B56" s="266"/>
+      <c r="C56" s="266"/>
       <c r="D56" s="16" t="s">
         <v>78</v>
       </c>
@@ -45166,9 +45166,9 @@
       <c r="M56" s="16"/>
       <c r="N56" s="15"/>
       <c r="O56" s="16"/>
-      <c r="R56" s="241"/>
-      <c r="S56" s="241"/>
-      <c r="T56" s="241"/>
+      <c r="R56" s="268"/>
+      <c r="S56" s="268"/>
+      <c r="T56" s="268"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="23"/>
@@ -45205,65 +45205,6 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -45280,6 +45221,65 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -45315,70 +45315,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="146" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="280" t="s">
+      <c r="A1" s="281" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="281"/>
-      <c r="C1" s="281"/>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
-      <c r="F1" s="281"/>
-      <c r="G1" s="281"/>
-      <c r="H1" s="281"/>
-      <c r="I1" s="281"/>
-      <c r="J1" s="281"/>
-      <c r="K1" s="281"/>
-      <c r="L1" s="282"/>
+      <c r="B1" s="282"/>
+      <c r="C1" s="282"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="282"/>
+      <c r="J1" s="282"/>
+      <c r="K1" s="282"/>
+      <c r="L1" s="283"/>
     </row>
     <row r="2" spans="1:12" s="147" customFormat="1">
       <c r="A2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="283"/>
-      <c r="C2" s="283"/>
-      <c r="D2" s="283"/>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="283"/>
-      <c r="I2" s="283"/>
-      <c r="J2" s="283"/>
-      <c r="K2" s="283"/>
-      <c r="L2" s="284"/>
+      <c r="B2" s="284"/>
+      <c r="C2" s="284"/>
+      <c r="D2" s="284"/>
+      <c r="E2" s="284"/>
+      <c r="F2" s="284"/>
+      <c r="G2" s="284"/>
+      <c r="H2" s="284"/>
+      <c r="I2" s="284"/>
+      <c r="J2" s="284"/>
+      <c r="K2" s="284"/>
+      <c r="L2" s="285"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="210" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="283" t="s">
+      <c r="B3" s="284" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="283"/>
-      <c r="D3" s="283"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="283"/>
-      <c r="G3" s="283"/>
-      <c r="H3" s="283"/>
-      <c r="I3" s="283"/>
-      <c r="J3" s="283"/>
-      <c r="K3" s="283"/>
-      <c r="L3" s="284"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="284"/>
+      <c r="E3" s="284"/>
+      <c r="F3" s="284"/>
+      <c r="G3" s="284"/>
+      <c r="H3" s="284"/>
+      <c r="I3" s="284"/>
+      <c r="J3" s="284"/>
+      <c r="K3" s="284"/>
+      <c r="L3" s="285"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="277" t="s">
+      <c r="A4" s="278" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="278"/>
-      <c r="C4" s="278"/>
-      <c r="D4" s="278"/>
-      <c r="E4" s="278"/>
-      <c r="F4" s="278"/>
-      <c r="G4" s="278"/>
-      <c r="H4" s="278"/>
-      <c r="I4" s="278"/>
-      <c r="J4" s="278"/>
-      <c r="K4" s="278"/>
-      <c r="L4" s="279"/>
+      <c r="B4" s="279"/>
+      <c r="C4" s="279"/>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+      <c r="I4" s="279"/>
+      <c r="J4" s="279"/>
+      <c r="K4" s="279"/>
+      <c r="L4" s="280"/>
     </row>
     <row r="5" spans="1:12" ht="105.75">
       <c r="A5" s="211" t="s">
@@ -50573,7 +50573,9 @@
       </c>
     </row>
     <row r="42" spans="1:22">
-      <c r="A42" s="3"/>
+      <c r="A42" s="183">
+        <v>41</v>
+      </c>
       <c r="B42" s="3">
         <f>Scoresheet!I43</f>
         <v>65</v>
@@ -50660,7 +50662,9 @@
       </c>
     </row>
     <row r="43" spans="1:22">
-      <c r="A43" s="3"/>
+      <c r="A43" s="183">
+        <v>42</v>
+      </c>
       <c r="B43" s="3">
         <f>Scoresheet!I44</f>
         <v>42</v>
@@ -50747,7 +50751,9 @@
       </c>
     </row>
     <row r="44" spans="1:22">
-      <c r="A44" s="3"/>
+      <c r="A44" s="183">
+        <v>43</v>
+      </c>
       <c r="B44" s="3">
         <f>Scoresheet!I45</f>
         <v>17</v>
